--- a/EHR_Compliance_Audit_Report.xlsx
+++ b/EHR_Compliance_Audit_Report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +49,12 @@
       <b val="1"/>
       <color rgb="001B365D"/>
       <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B365D"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -113,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,12 +129,28 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -203,6 +225,120 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Distribution of Compliance Issues</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Executive Summary'!B10</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Executive Summary'!$A$11:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Executive Summary'!$B$11:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3420000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -494,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
@@ -511,7 +647,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: 2026-05-22 11:27</t>
+          <t>Report Generated: 2026-05-22 19:27</t>
         </is>
       </c>
     </row>
@@ -533,11 +669,74 @@
         <v>30</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>26</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Data Error Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Issue Type</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Missing Billing Code</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Timeline Discrepancy</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -547,706 +746,1030 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Patient ID</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Issue Type</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Current Value</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Action Required</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>PT1001</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>PT1002</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="n">
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n">
         <v>987654321</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>PT1003</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>PT1003</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>PT1004</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sarah Jenkins </t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>PT1005</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n">
         <v>987654321</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>PT1006</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>PT1006</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>PT1007</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sarah Jenkins </t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>PT1008</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
         <v/>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>PT1009</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sarah Jenkins </t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>PT1010</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
         <v>987654321</v>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>PT1011</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sarah Jenkins </t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>PT1012</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n">
         <v/>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>PT1012</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>discharge_date</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Timeline Discrepancy</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Adm: 2026-05-13 | Dis: 2026-05-10</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Review chart timeline; correct clinical dates.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>PT1013</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>PT1014</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="n">
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v/>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>PT1014</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>PT1015</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>987654321</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>PT1016</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n">
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
         <v>987654321</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>PT1017</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>PT1018</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
         <v/>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>PT1019</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>987654321</v>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>PT1020</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>PT1020</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Dr. Sarah Jenkins</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>PT1021</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n">
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
         <v>987654321</v>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>PT1022</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v/>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>PT1022</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>PT1023</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v/>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>PT1024</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="n">
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
         <v/>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>PT1025</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>987654321</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>PT1025</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>PT1026</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n">
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="n">
         <v/>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>PT1027</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sarah Jenkins </t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>PT1028</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="n">
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>987654321</v>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>PT1029</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>provider_npi</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>Invalid/Missing NPI</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Invalid/Missing NPI</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="n">
         <v/>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>Verify provider NPI profile and update registry.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>PT1029</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>icd_10_code</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>Missing Billing Code</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>BLANK</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr">
         <is>
           <t>Route back to medical coding team for chart review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>PT1030</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>provider_name</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Duplicate Provider Profile</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dr. Sarah Jenkins </t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Duplicate NPI mapping found. Merge clinician credentials in registry.</t>
         </is>
       </c>
     </row>
